--- a/data/trans_dic/P19C04-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19C04-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por la extracción de algún diente o muela</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por la extracción de algún diente o muela (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,93; 24,83</t>
+          <t>18,14; 25,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,27; 34,64</t>
+          <t>27,08; 34,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,2; 25,74</t>
+          <t>18,26; 25,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,96; 26,14</t>
+          <t>19,02; 26,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,03; 16,76</t>
+          <t>10,81; 16,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,78; 20,93</t>
+          <t>14,54; 20,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,64; 18,22</t>
+          <t>12,1; 17,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,62; 17,57</t>
+          <t>13,53; 17,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,08; 19,85</t>
+          <t>15,06; 19,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,72; 26,58</t>
+          <t>21,58; 26,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,98; 20,6</t>
+          <t>15,95; 20,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,92; 20,82</t>
+          <t>16,94; 20,96</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,93; 23,9</t>
+          <t>17,89; 24,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,32; 29,53</t>
+          <t>23,55; 29,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,38; 18,68</t>
+          <t>13,47; 18,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,95; 14,55</t>
+          <t>5,96; 14,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,96; 14,64</t>
+          <t>9,95; 14,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,82; 22,52</t>
+          <t>17,12; 22,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,73; 15,41</t>
+          <t>10,76; 15,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,36; 13,82</t>
+          <t>10,25; 13,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,42; 18,32</t>
+          <t>14,53; 18,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,62; 25,05</t>
+          <t>20,64; 24,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,8; 16,32</t>
+          <t>12,77; 16,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,85; 13,42</t>
+          <t>7,07; 13,41</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,61; 23,46</t>
+          <t>16,49; 23,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,77; 28,3</t>
+          <t>21,24; 28,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,54; 22,51</t>
+          <t>15,99; 22,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,68; 13,96</t>
+          <t>8,62; 13,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,44; 20,98</t>
+          <t>14,49; 20,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,92; 18,68</t>
+          <t>13,08; 19,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,04; 14,54</t>
+          <t>9,02; 14,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 9,17</t>
+          <t>3,16; 9,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,54; 21,2</t>
+          <t>16,34; 20,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,12; 22,5</t>
+          <t>17,91; 22,46</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,11; 17,27</t>
+          <t>13,07; 17,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,86; 10,23</t>
+          <t>5,29; 10,3</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,55; 21,2</t>
+          <t>15,27; 20,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,5; 21,47</t>
+          <t>15,89; 21,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,75; 18,91</t>
+          <t>13,79; 19,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,7; 18,8</t>
+          <t>13,65; 18,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,38; 18,63</t>
+          <t>13,46; 18,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,52; 19,57</t>
+          <t>14,57; 19,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,78; 15,28</t>
+          <t>10,75; 15,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 11,57</t>
+          <t>7,7; 11,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,97; 18,84</t>
+          <t>15,1; 18,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,86; 19,56</t>
+          <t>15,77; 19,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,87; 16,36</t>
+          <t>12,8; 16,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,82; 14,08</t>
+          <t>11,0; 14,32</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,37; 21,65</t>
+          <t>18,3; 21,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,07; 26,49</t>
+          <t>23,2; 26,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,39; 19,45</t>
+          <t>16,41; 19,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,18; 16,24</t>
+          <t>11,22; 16,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,28; 15,96</t>
+          <t>13,46; 16,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,21; 18,88</t>
+          <t>16,13; 18,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,7; 14,42</t>
+          <t>11,64; 14,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,63; 11,67</t>
+          <t>8,53; 11,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,06; 18,26</t>
+          <t>16,14; 18,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,98; 22,12</t>
+          <t>19,87; 22,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,36; 16,34</t>
+          <t>14,4; 16,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,75; 13,57</t>
+          <t>10,93; 13,63</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por la extracción de algún diente o muela</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por la extracción de algún diente o muela (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>85673; 118635</t>
+          <t>86666; 121847</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>165214; 209873</t>
+          <t>164074; 210547</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95574; 135148</t>
+          <t>95870; 132758</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>115921; 159807</t>
+          <t>116290; 159647</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>59375; 90194</t>
+          <t>58160; 88476</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93944; 133089</t>
+          <t>92441; 132134</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63358; 99163</t>
+          <t>65883; 97496</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>88757; 114461</t>
+          <t>88147; 115059</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>153160; 201628</t>
+          <t>152978; 201507</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>269650; 330011</t>
+          <t>267999; 331416</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>170868; 220259</t>
+          <t>170526; 221791</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>213705; 262925</t>
+          <t>213962; 264703</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>129452; 172568</t>
+          <t>129194; 173717</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>202161; 256049</t>
+          <t>204173; 255396</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>109186; 152458</t>
+          <t>109965; 154636</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69425; 169732</t>
+          <t>69541; 171943</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80080; 117745</t>
+          <t>79984; 117767</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>150868; 201985</t>
+          <t>153503; 199541</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>92925; 133532</t>
+          <t>93261; 133933</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>97645; 130184</t>
+          <t>96604; 128545</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>220135; 279681</t>
+          <t>221736; 276794</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>363745; 441838</t>
+          <t>364095; 440725</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>215350; 274562</t>
+          <t>214802; 277279</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>165591; 283022</t>
+          <t>149109; 282768</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>90520; 127900</t>
+          <t>89858; 128008</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>132107; 179993</t>
+          <t>135093; 182575</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85522; 123902</t>
+          <t>88014; 126272</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59542; 95825</t>
+          <t>59183; 93362</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>84404; 122655</t>
+          <t>84717; 121329</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87650; 126737</t>
+          <t>88726; 130074</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>52415; 84306</t>
+          <t>52309; 83566</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28023; 84535</t>
+          <t>29129; 84184</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>186852; 239487</t>
+          <t>184591; 235179</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>238220; 295826</t>
+          <t>235465; 295256</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>148184; 195224</t>
+          <t>147707; 201456</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>78186; 164519</t>
+          <t>85135; 165607</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>110387; 150481</t>
+          <t>108404; 147620</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>124900; 172992</t>
+          <t>128035; 175596</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>106234; 146125</t>
+          <t>106515; 146939</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>121794; 167144</t>
+          <t>121367; 168263</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>108918; 151677</t>
+          <t>109544; 150974</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>135666; 182837</t>
+          <t>136110; 181449</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>94436; 133856</t>
+          <t>94122; 136015</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>82338; 122931</t>
+          <t>81866; 120974</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>228044; 287134</t>
+          <t>230043; 287594</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>275926; 340307</t>
+          <t>274396; 338254</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212067; 269727</t>
+          <t>210912; 267544</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>211253; 274843</t>
+          <t>214605; 279588</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>450878; 531386</t>
+          <t>449175; 530224</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>672392; 772075</t>
+          <t>676315; 774731</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>436630; 518235</t>
+          <t>437264; 516550</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>374856; 544619</t>
+          <t>376258; 540180</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>364094; 437561</t>
+          <t>368865; 439813</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>509695; 593783</t>
+          <t>507321; 592332</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>335473; 413296</t>
+          <t>333507; 410704</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>308764; 417583</t>
+          <t>305337; 415367</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>834415; 948895</t>
+          <t>838333; 946159</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1210693; 1340636</t>
+          <t>1204086; 1338789</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>794359; 903583</t>
+          <t>796671; 906223</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>745530; 940970</t>
+          <t>757706; 944760</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C04-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19C04-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,14; 25,5</t>
+          <t>18,01; 25,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,08; 34,75</t>
+          <t>27,08; 34,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,26; 25,29</t>
+          <t>18,19; 25,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,02; 26,12</t>
+          <t>19,52; 26,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,81; 16,44</t>
+          <t>10,78; 16,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,54; 20,78</t>
+          <t>14,69; 20,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,1; 17,91</t>
+          <t>12,02; 18,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,53; 17,66</t>
+          <t>13,24; 17,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,06; 19,83</t>
+          <t>15,11; 19,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,58; 26,69</t>
+          <t>21,63; 26,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,95; 20,74</t>
+          <t>15,81; 20,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,94; 20,96</t>
+          <t>16,9; 20,83</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,89; 24,06</t>
+          <t>17,74; 23,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,55; 29,46</t>
+          <t>23,25; 29,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,47; 18,94</t>
+          <t>13,61; 18,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,96; 14,74</t>
+          <t>12,49; 17,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,95; 14,64</t>
+          <t>10,01; 14,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,12; 22,25</t>
+          <t>16,89; 22,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,76; 15,46</t>
+          <t>10,78; 15,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,25; 13,64</t>
+          <t>10,59; 14,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,53; 18,13</t>
+          <t>14,53; 18,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,64; 24,99</t>
+          <t>20,93; 24,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,77; 16,48</t>
+          <t>12,73; 16,51</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,07; 13,41</t>
+          <t>12,0; 14,88</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,49; 23,48</t>
+          <t>16,78; 23,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,24; 28,71</t>
+          <t>21,48; 28,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,99; 22,94</t>
+          <t>16,05; 22,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,62; 13,6</t>
+          <t>9,35; 14,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,49; 20,75</t>
+          <t>14,42; 20,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,08; 19,17</t>
+          <t>13,04; 19,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,02; 14,41</t>
+          <t>8,96; 14,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,16; 9,13</t>
+          <t>7,04; 10,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,34; 20,82</t>
+          <t>16,65; 21,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,91; 22,46</t>
+          <t>17,56; 22,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,07; 17,83</t>
+          <t>13,08; 17,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,29; 10,3</t>
+          <t>8,87; 11,9</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,27; 20,8</t>
+          <t>15,43; 20,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,89; 21,79</t>
+          <t>15,81; 21,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,79; 19,02</t>
+          <t>13,86; 18,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,65; 18,93</t>
+          <t>14,89; 19,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,46; 18,55</t>
+          <t>13,55; 18,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,57; 19,42</t>
+          <t>14,6; 19,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,75; 15,53</t>
+          <t>10,64; 15,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,7; 11,38</t>
+          <t>9,0; 12,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,1; 18,87</t>
+          <t>15,0; 18,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,77; 19,44</t>
+          <t>15,68; 19,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,8; 16,23</t>
+          <t>12,88; 16,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,0; 14,32</t>
+          <t>12,25; 15,11</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,3; 21,6</t>
+          <t>18,43; 21,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,2; 26,58</t>
+          <t>22,96; 26,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,41; 19,39</t>
+          <t>16,5; 19,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,22; 16,11</t>
+          <t>14,83; 17,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,46; 16,05</t>
+          <t>13,43; 16,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,13; 18,83</t>
+          <t>16,28; 19,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,64; 14,33</t>
+          <t>11,77; 14,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,53; 11,61</t>
+          <t>10,7; 12,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,14; 18,21</t>
+          <t>16,14; 18,29</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,87; 22,09</t>
+          <t>19,9; 22,08</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,4; 16,39</t>
+          <t>14,29; 16,27</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,93; 13,63</t>
+          <t>13,05; 14,63</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>137010</t>
+          <t>148971</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>100950</t>
+          <t>107869</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>237960</t>
+          <t>256840</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>86666; 121847</t>
+          <t>86057; 121011</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>164074; 210547</t>
+          <t>164101; 210072</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95870; 132758</t>
+          <t>95494; 135289</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>116290; 159647</t>
+          <t>128741; 173483</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>58160; 88476</t>
+          <t>58007; 89414</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92441; 132134</t>
+          <t>93396; 132149</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65883; 97496</t>
+          <t>65436; 98691</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>88147; 115059</t>
+          <t>93487; 123117</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>152978; 201507</t>
+          <t>153491; 199000</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>267999; 331416</t>
+          <t>268598; 331670</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>170526; 221791</t>
+          <t>169017; 220191</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>213962; 264703</t>
+          <t>230863; 284536</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>128954</t>
+          <t>150425</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>111968</t>
+          <t>127498</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>240922</t>
+          <t>277923</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>129194; 173717</t>
+          <t>128096; 172467</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>204173; 255396</t>
+          <t>201571; 253885</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>109965; 154636</t>
+          <t>111101; 153228</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69541; 171943</t>
+          <t>126943; 175358</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>79984; 117767</t>
+          <t>80521; 118169</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>153503; 199541</t>
+          <t>151448; 200168</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>93261; 133933</t>
+          <t>93404; 134213</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>96604; 128545</t>
+          <t>110994; 147075</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>221736; 276794</t>
+          <t>221806; 278979</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>364095; 440725</t>
+          <t>369185; 440556</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>214802; 277279</t>
+          <t>214254; 277810</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>149109; 282768</t>
+          <t>247679; 307021</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75132</t>
+          <t>91710</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>60376</t>
+          <t>69830</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>135508</t>
+          <t>161541</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>89858; 128008</t>
+          <t>91478; 128622</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>135093; 182575</t>
+          <t>136641; 180951</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>88014; 126272</t>
+          <t>88316; 124915</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59183; 93362</t>
+          <t>72406; 115674</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>84717; 121329</t>
+          <t>84285; 120890</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88726; 130074</t>
+          <t>88446; 129205</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>52309; 83566</t>
+          <t>51965; 84135</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29129; 84184</t>
+          <t>55995; 85816</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>184591; 235179</t>
+          <t>188047; 241276</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>235465; 295256</t>
+          <t>230883; 293314</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>147707; 201456</t>
+          <t>147843; 196380</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>85135; 165607</t>
+          <t>139193; 186807</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143882</t>
+          <t>164811</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>103107</t>
+          <t>111918</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>246989</t>
+          <t>276729</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>108404; 147620</t>
+          <t>109495; 148770</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>128035; 175596</t>
+          <t>127343; 172707</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>106515; 146939</t>
+          <t>107069; 146454</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>121367; 168263</t>
+          <t>140975; 189172</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>109544; 150974</t>
+          <t>110258; 150655</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>136110; 181449</t>
+          <t>136385; 182513</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>94122; 136015</t>
+          <t>93191; 136276</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>81866; 120974</t>
+          <t>96830; 129497</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>230043; 287594</t>
+          <t>228486; 286411</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>274396; 338254</t>
+          <t>272741; 336956</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>210912; 267544</t>
+          <t>212306; 268702</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>214605; 279588</t>
+          <t>247879; 305627</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>484977</t>
+          <t>555917</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>376402</t>
+          <t>417116</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>861379</t>
+          <t>973032</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>449175; 530224</t>
+          <t>452315; 532460</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>676315; 774731</t>
+          <t>669120; 766749</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>437264; 516550</t>
+          <t>439636; 519767</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>376258; 540180</t>
+          <t>503648; 599034</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>368865; 439813</t>
+          <t>368079; 443924</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>507321; 592332</t>
+          <t>512065; 603803</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>333507; 410704</t>
+          <t>337268; 413031</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>305337; 415367</t>
+          <t>388067; 448988</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838333; 946159</t>
+          <t>838459; 950149</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1204086; 1338789</t>
+          <t>1206019; 1337771</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>796671; 906223</t>
+          <t>790208; 899820</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>757706; 944760</t>
+          <t>916155; 1027041</t>
         </is>
       </c>
     </row>
